--- a/Checklist_RIESGOS_CEDIS.xlsx
+++ b/Checklist_RIESGOS_CEDIS.xlsx
@@ -1062,7 +1062,7 @@
     <row r="1" ht="20" customHeight="1" s="57">
       <c r="A1" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FICHA DEL CENTRO DE DISTRIBUCIÓN </t>
+          <t xml:space="preserve">  FICHA DEL CENTRO DE DISTRIBUCIÓN</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C2" s="54" t="inlineStr">
         <is>
-          <t>ESTRUCTURA Y CUBIERTA. Columnas sin impacto ni corrosión y con protectores; canales, bajantes y tragantes limpios antes de lluvias.</t>
+          <t>ESTRUCTURA Y CUBIERTA. Columnas sin impactos ni corrosión y con protectores instalados; canales, bajantes y tragantes limpios antes de lluvias.</t>
         </is>
       </c>
       <c r="D2" s="47" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C16" s="54" t="inlineStr">
         <is>
-          <t>OCUPACIÓN Y PASILLOS LIBRES. % de ocupación vs. capacidad y pasillos, salidas, extintores, hidrantes y tableros sin obstrucción.</t>
+          <t>OCUPACIÓN Y PASILLOS LIBRES. % de ocupación frente a la capacidad instalada; pasillos, salidas, extintores, hidrantes y tableros sin obstrucción.</t>
         </is>
       </c>
       <c r="D16" s="47" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C28" s="54" t="inlineStr">
         <is>
-          <t>AGUA Y ROCIADORES. Válvulas de control abiertas y aseguradas, presiones correctas, bomba que arranca y tanque con su nivel.</t>
+          <t>AGUA Y ROCIADORES. Válvulas de control abiertas y aseguradas, presiones correctas, bomba que arranca en la prueba y tanque de reserva en su nivel.</t>
         </is>
       </c>
       <c r="D28" s="47" t="inlineStr">
@@ -2859,7 +2859,7 @@
       <c r="M30" s="12" t="n"/>
       <c r="N30" s="13" t="n"/>
     </row>
-    <row r="31" ht="46" customHeight="1" s="57">
+    <row r="31" ht="48" customHeight="1" s="57">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>R-30</t>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="C31" s="54" t="inlineStr">
         <is>
-          <t>INFLAMABLES, AEROSOLES Y RESIDUOS. Cuarto o gabinete dedicado con cantidades máximas, dique y ventilación; patio de estibas separado del edificio y residuos evacuados.</t>
+          <t>INFLAMABLES, AEROSOLES Y RESIDUOS. Cuarto o gabinete dedicado con cantidades máximas definidas, dique de contención y ventilación; patio de estibas separado del edificio y residuos evacuados.</t>
         </is>
       </c>
       <c r="D31" s="47" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C32" s="54" t="inlineStr">
         <is>
-          <t>TRABAJOS EN CALIENTE E INSTALACIÓN ELÉCTRICA. Permiso con vigía de fuego y área despejada 11 m; sin extensiones improvisadas y tableros cerrados, rotulados y despejados.</t>
+          <t>TRABAJOS EN CALIENTE E INSTALACIÓN ELÉCTRICA. Permiso con vigía de fuego y área despejada 11 m a la redonda; sin extensiones improvisadas y tableros cerrados, rotulados y despejados.</t>
         </is>
       </c>
       <c r="D32" s="47" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C36" s="54" t="inlineStr">
         <is>
-          <t>AGUA Y VIENTO. Capacidad de drenaje y drenajes de emergencia, fijaciones de cubierta, elementos sueltos en patio y producto sensible fuera del piso en zona inundable.</t>
+          <t>AGUA Y VIENTO. Capacidad de evacuación de agua y drenajes de emergencia, fijaciones de cubierta, elementos sueltos en patio y producto sensible fuera del piso en zona inundable.</t>
         </is>
       </c>
       <c r="D36" s="47" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C39" s="54" t="inlineStr">
         <is>
-          <t>RESPALDO DE ENERGÍA Y REFRIGERACIÓN. Planta probada con carga, autonomía y cobertura de circuitos críticos; detección de fuga y mantenimiento del sistema de frío.</t>
+          <t>RESPALDO DE ENERGÍA Y REFRIGERACIÓN. Planta eléctrica probada con carga, con autonomía suficiente y cobertura de los circuitos críticos; detección de fuga y mantenimiento del sistema de frío.</t>
         </is>
       </c>
       <c r="D39" s="47" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C43" s="54" t="inlineStr">
         <is>
-          <t>PROTECCIÓN DE LA CARGA. Inspección del contenedor antes del cargue, control y trazabilidad de sellos de alta seguridad y validación de identidad del conductor contra la programación.</t>
+          <t>PROTECCIÓN DE LA CARGA. Inspección del contenedor antes del cargue, control y trazabilidad de los sellos de alta seguridad; validación de la identidad del conductor contra la programación.</t>
         </is>
       </c>
       <c r="D43" s="47" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C50" s="54" t="inlineStr">
         <is>
-          <t>HIGIENE, TEMPERATURA Y ATENCIÓN MÉDICA. Mediciones higiénicas vigentes, control de exposición a frío y calor, permiso para espacios confinados y contenedores fumigados, y botiquines y camillas por turno.</t>
+          <t>HIGIENE, TEMPERATURA Y ATENCIÓN MÉDICA. Mediciones higiénicas vigentes, control de exposición a frío y calor, permiso para espacios confinados y contenedores fumigados; botiquines y camillas disponibles por turno.</t>
         </is>
       </c>
       <c r="D50" s="47" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="C53" s="54" t="inlineStr">
         <is>
-          <t>SEGREGACIÓN Y MERCANCÍAS PELIGROSAS. Matriz de compatibilidad, químicos separados de alimentos, alérgenos segregados, rotulado por clase ONU, fichas de seguridad accesibles y kit de derrames.</t>
+          <t>SEGREGACIÓN Y MERCANCÍAS PELIGROSAS. Matriz de compatibilidad, químicos separados de alimentos, alérgenos segregados, rotulado por clase ONU, fichas de datos de seguridad accesibles y kit de derrames.</t>
         </is>
       </c>
       <c r="D53" s="47" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C59" s="54" t="inlineStr">
         <is>
-          <t>OPERADOR LOGÍSTICO Y TRANSPORTISTAS. Contrato con indicadores y requisitos de seguridad y salud en el trabajo, auditoría del tercero, y documentación y estado del vehículo verificados antes del cargue.</t>
+          <t>OPERADOR LOGÍSTICO Y TRANSPORTISTAS. Contrato con indicadores y requisitos de seguridad y salud en el trabajo, auditoría del tercero, y verificación de la documentación y del estado del vehículo antes del cargue.</t>
         </is>
       </c>
       <c r="D59" s="47" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C60" s="54" t="inlineStr">
         <is>
-          <t>PERMISOS Y CUMPLIMIENTO DEL SISTEMA DE GESTIÓN DE SEGURIDAD Y SALUD EN EL TRABAJO. Matriz de requisitos legales con fechas de vencimiento (bomberos, sanitario, ambiental, uso de suelo) y autoevaluación del sistema, con su plan de trabajo ejecutado.</t>
+          <t>PERMISOS Y CUMPLIMIENTO DEL SISTEMA DE GESTIÓN DE SEGURIDAD Y SALUD EN EL TRABAJO. Matriz de requisitos legales con fechas de vencimiento (bomberos, sanitario, ambiental, uso de suelo) y autoevaluación del sistema con su plan de trabajo anual ejecutado.</t>
         </is>
       </c>
       <c r="D60" s="47" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C63" s="54" t="inlineStr">
         <is>
-          <t>LECCIONES APRENDIDAS Y CIERRE DE ACCIONES. Investigación de todos los eventos incluidos los casi-accidentes, causa raíz, cierre y verificación de eficacia.</t>
+          <t>LECCIONES APRENDIDAS Y CIERRE DE ACCIONES. Investigación de todos los eventos, incluidos los casi-accidentes, con causa raíz, cierre y verificación de eficacia.</t>
         </is>
       </c>
       <c r="D63" s="47" t="inlineStr">
@@ -6012,7 +6012,7 @@
     <row r="27" ht="20" customHeight="1" s="57">
       <c r="A27" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MATRIZ 5 × 5   (filas = Probabilidad · columnas = Impacto)</t>
+          <t xml:space="preserve">  MATRIZ 5 × 5 (filas = Probabilidad · columnas = Impacto)</t>
         </is>
       </c>
     </row>
